--- a/API.xlsx
+++ b/API.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git Repo\Company-Registration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{65B36F7C-5425-40D6-8A95-58B3D8329609}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{468112AD-3CEE-4A23-93B2-6A7E480E096E}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{9A6E912D-777C-46C6-A7EE-14F6AFAACB46}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="124">
   <si>
     <t>Sr No</t>
   </si>
@@ -286,13 +286,472 @@
   </si>
   <si>
     <t xml:space="preserve">  }</t>
+  </si>
+  <si>
+    <t>System User</t>
+  </si>
+  <si>
+    <t>https://localhost:44378/api/SystemUser/CreateUser</t>
+  </si>
+  <si>
+    <t>create{</t>
+  </si>
+  <si>
+    <r>
+      <t>    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"data"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Id"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF098658"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"UserName"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0451A5"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"name"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"EmailAddress"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF0451A5"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>null</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Password"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF0451A5"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>null</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"AccountStatus"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0451A5"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"ACTIVE"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"UserRole"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0451A5"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Admin"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"IsUpdate"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF0451A5"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>true</t>
+    </r>
+  </si>
+  <si>
+    <t>    },</t>
+  </si>
+  <si>
+    <r>
+      <t>    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"IsSuccess"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF0451A5"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Message"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0451A5"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"User updated successfully."</t>
+    </r>
+  </si>
+  <si>
+    <t>Post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "Id": 0,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "UserName": "adminuser",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "EmailAddress": "admin123@example.com",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "Password": "123456",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "AccountStatus": "ACTIVE",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "UserRole": "ADMIN",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "IsUpdate": false</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "IsSuccess": true,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "Message": "User created successfully."</t>
+  </si>
+  <si>
+    <t>  "userName": "adminuser",</t>
+  </si>
+  <si>
+    <t>  "emailAddress": "admin@example.com",</t>
+  </si>
+  <si>
+    <t>  "password": "123456",</t>
+  </si>
+  <si>
+    <t>  "userRole": "ADMIN",</t>
+  </si>
+  <si>
+    <t>  "accountStatus": "ACTIVE",</t>
+  </si>
+  <si>
+    <t>  "isUpdate": false</t>
+  </si>
+  <si>
+    <t>PUT</t>
+  </si>
+  <si>
+    <t>Update {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "id": 1,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "userName": "name",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "userRole": "Admin",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "accountStatus": "ACTIVE",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "isUpdate": true</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -321,6 +780,43 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF212121"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFA31515"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0451A5"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF0451A5"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF098658"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -396,7 +892,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -404,9 +900,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -432,6 +925,60 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -748,7 +1295,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54E5AA88-04D7-418A-AE8C-58C683F9EEB3}">
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
@@ -756,7 +1303,7 @@
     <col min="3" max="3" width="56" style="1" customWidth="1"/>
     <col min="4" max="4" width="23" style="1" customWidth="1"/>
     <col min="5" max="5" width="48.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="38.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="58" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -780,19 +1327,19 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="A2" s="15">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="4" t="s">
@@ -800,130 +1347,130 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="9" t="s">
+      <c r="A3" s="16"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="9" t="s">
+      <c r="A4" s="16"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="10" t="s">
+      <c r="A5" s="16"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="10" t="s">
+    <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="9"/>
+      <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="9" t="s">
+      <c r="A7" s="16"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="9"/>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="9" t="s">
+      <c r="A8" s="16"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="9"/>
-    </row>
-    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="10" t="s">
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="16"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="9"/>
-    </row>
-    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="10" t="s">
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="16"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="9"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="9" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="9"/>
+      <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="9" t="s">
+      <c r="A12" s="16"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="9"/>
+      <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="10" t="s">
+      <c r="A13" s="16"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="9"/>
+      <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="13" t="s">
+      <c r="A14" s="17"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="13"/>
+      <c r="F14" s="12"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -932,100 +1479,100 @@
       <c r="B15" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="13" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F15" s="4"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="10" t="s">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="10" t="s">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="9" t="s">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9" t="s">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="9" t="s">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9" t="s">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9" t="s">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="13" t="s">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1036,696 +1583,1018 @@
       <c r="B24" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="13" t="s">
         <v>35</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E24" s="6"/>
+      <c r="E24" s="5"/>
       <c r="F24" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="9" t="s">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="9" t="s">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9" t="s">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9" t="s">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9" t="s">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9" t="s">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9" t="s">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9" t="s">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9" t="s">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9" t="s">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9" t="s">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9" t="s">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9" t="s">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9" t="s">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9" t="s">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9" t="s">
+      <c r="A41" s="8"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="9"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9" t="s">
+      <c r="A42" s="8"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9" t="s">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9" t="s">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9" t="s">
+      <c r="A45" s="8"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9" t="s">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9" t="s">
+      <c r="A47" s="8"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9" t="s">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9" t="s">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9" t="s">
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9" t="s">
+      <c r="A51" s="8"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="9"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9" t="s">
+      <c r="A52" s="8"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="9"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="9"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9" t="s">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="9"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9" t="s">
+      <c r="A55" s="8"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="9"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9" t="s">
+      <c r="A56" s="8"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="9"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9" t="s">
+      <c r="A57" s="8"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="8" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="9"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9" t="s">
+      <c r="A58" s="8"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="9"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9" t="s">
+      <c r="A59" s="8"/>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="9"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
+      <c r="A60" s="8"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="9"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9" t="s">
+      <c r="A61" s="8"/>
+      <c r="B61" s="8"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="8" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="9"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9" t="s">
+      <c r="A62" s="8"/>
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="9"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9" t="s">
+      <c r="A63" s="8"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="9"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9" t="s">
+      <c r="A64" s="8"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="9"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9" t="s">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="9"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9" t="s">
+      <c r="A66" s="8"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="9"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9" t="s">
+      <c r="A67" s="8"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="8" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="9"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9" t="s">
+      <c r="A68" s="8"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="9"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9" t="s">
+      <c r="A69" s="8"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="8" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="9"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9" t="s">
+      <c r="A70" s="8"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="8" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="9"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9" t="s">
+      <c r="A71" s="8"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="9"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9" t="s">
+      <c r="A72" s="8"/>
+      <c r="B72" s="8"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="8" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="9"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9" t="s">
+      <c r="A73" s="8"/>
+      <c r="B73" s="8"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="8"/>
+      <c r="F73" s="8" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="9"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9" t="s">
+      <c r="A74" s="8"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="9"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9" t="s">
+      <c r="A75" s="8"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="9"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9" t="s">
+      <c r="A76" s="8"/>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="9"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9" t="s">
+      <c r="A77" s="8"/>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="8" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="9"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9" t="s">
+      <c r="A78" s="8"/>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="9"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9" t="s">
+      <c r="A79" s="8"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="9"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
+      <c r="A80" s="8"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="8"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="8"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="9"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
+      <c r="A81" s="8"/>
+      <c r="B81" s="8"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="8"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="9"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9" t="s">
+      <c r="A82" s="8"/>
+      <c r="B82" s="8"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="8" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="9"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
-      <c r="F83" s="9" t="s">
+      <c r="A83" s="8"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="8" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="9"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9" t="s">
+      <c r="A84" s="8"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="8" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="9"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="9"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="9"/>
-      <c r="F85" s="9" t="s">
+      <c r="A85" s="8"/>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="9"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="9"/>
-      <c r="D86" s="9"/>
-      <c r="E86" s="9"/>
-      <c r="F86" s="9" t="s">
+      <c r="A86" s="8"/>
+      <c r="B86" s="8"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="8" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="9"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="9"/>
-      <c r="D87" s="9"/>
-      <c r="E87" s="9"/>
-      <c r="F87" s="9" t="s">
+      <c r="A87" s="8"/>
+      <c r="B87" s="8"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="8"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="8" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="9"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="9"/>
-      <c r="D88" s="9"/>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9"/>
+      <c r="A88" s="8"/>
+      <c r="B88" s="8"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="8"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="8"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="9"/>
-      <c r="B89" s="9"/>
-      <c r="C89" s="9"/>
-      <c r="D89" s="9"/>
-      <c r="E89" s="9"/>
-      <c r="F89" s="9" t="s">
+      <c r="A89" s="8"/>
+      <c r="B89" s="8"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="8"/>
+      <c r="F89" s="8" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="9"/>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
-      <c r="F90" s="9" t="s">
+      <c r="A90" s="8"/>
+      <c r="B90" s="8"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="8"/>
+      <c r="E90" s="8"/>
+      <c r="F90" s="8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="9"/>
-      <c r="B91" s="9"/>
-      <c r="C91" s="9"/>
-      <c r="D91" s="9"/>
-      <c r="E91" s="9"/>
-      <c r="F91" s="9" t="s">
+      <c r="A91" s="8"/>
+      <c r="B91" s="8"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="8"/>
+      <c r="F91" s="8" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="9"/>
-      <c r="B92" s="9"/>
-      <c r="C92" s="9"/>
-      <c r="D92" s="9"/>
-      <c r="E92" s="9"/>
-      <c r="F92" s="9" t="s">
+      <c r="A92" s="8"/>
+      <c r="B92" s="8"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="8"/>
+      <c r="E92" s="8"/>
+      <c r="F92" s="8" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="13"/>
-      <c r="B93" s="13"/>
-      <c r="C93" s="13"/>
-      <c r="D93" s="13"/>
-      <c r="E93" s="13"/>
-      <c r="F93" s="13" t="s">
+      <c r="A93" s="12"/>
+      <c r="B93" s="12"/>
+      <c r="C93" s="12"/>
+      <c r="D93" s="12"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="12" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="94" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="18">
+        <v>4</v>
+      </c>
+      <c r="B94" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C94" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="D94" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="E94" s="4"/>
+      <c r="F94" s="27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="19"/>
+      <c r="B95" s="16"/>
+      <c r="C95" s="31"/>
+      <c r="D95" s="16"/>
+      <c r="E95" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F95" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="19"/>
+      <c r="B96" s="16"/>
+      <c r="C96" s="31"/>
+      <c r="D96" s="16"/>
+      <c r="E96" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F96" s="28" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="19"/>
+      <c r="B97" s="16"/>
+      <c r="C97" s="31"/>
+      <c r="D97" s="16"/>
+      <c r="E97" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="F97" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="19"/>
+      <c r="B98" s="16"/>
+      <c r="C98" s="31"/>
+      <c r="D98" s="16"/>
+      <c r="E98" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F98" s="28" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="19"/>
+      <c r="B99" s="16"/>
+      <c r="C99" s="31"/>
+      <c r="D99" s="16"/>
+      <c r="E99" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F99" s="28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="19"/>
+      <c r="B100" s="16"/>
+      <c r="C100" s="31"/>
+      <c r="D100" s="16"/>
+      <c r="E100" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F100" s="28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="19"/>
+      <c r="B101" s="16"/>
+      <c r="C101" s="31"/>
+      <c r="D101" s="16"/>
+      <c r="E101" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F101" s="28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="19"/>
+      <c r="B102" s="16"/>
+      <c r="C102" s="31"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F102" s="9"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="19"/>
+      <c r="B103" s="16"/>
+      <c r="C103" s="31"/>
+      <c r="D103" s="16"/>
+      <c r="E103" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F103" s="8"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="19"/>
+      <c r="B104" s="16"/>
+      <c r="C104" s="31"/>
+      <c r="D104" s="16"/>
+      <c r="E104" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F104" s="8"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="19"/>
+      <c r="B105" s="16"/>
+      <c r="C105" s="31"/>
+      <c r="D105" s="16"/>
+      <c r="E105" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F105" s="8"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="19"/>
+      <c r="B106" s="16"/>
+      <c r="C106" s="31"/>
+      <c r="D106" s="16"/>
+      <c r="E106" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="F106" s="8"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="19"/>
+      <c r="B107" s="16"/>
+      <c r="C107" s="31"/>
+      <c r="D107" s="17"/>
+      <c r="E107" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F107" s="12"/>
+    </row>
+    <row r="108" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="15">
+        <v>5</v>
+      </c>
+      <c r="B108" s="16"/>
+      <c r="C108" s="31"/>
+      <c r="D108" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="E108" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="16"/>
+      <c r="B109" s="16"/>
+      <c r="C109" s="31"/>
+      <c r="D109" s="16"/>
+      <c r="E109" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="16"/>
+      <c r="B110" s="16"/>
+      <c r="C110" s="31"/>
+      <c r="D110" s="16"/>
+      <c r="E110" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="16"/>
+      <c r="B111" s="16"/>
+      <c r="C111" s="31"/>
+      <c r="D111" s="16"/>
+      <c r="E111" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="16"/>
+      <c r="B112" s="16"/>
+      <c r="C112" s="31"/>
+      <c r="D112" s="16"/>
+      <c r="E112" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="16"/>
+      <c r="B113" s="16"/>
+      <c r="C113" s="31"/>
+      <c r="D113" s="16"/>
+      <c r="E113" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="16"/>
+      <c r="B114" s="16"/>
+      <c r="C114" s="31"/>
+      <c r="D114" s="16"/>
+      <c r="E114" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="16"/>
+      <c r="B115" s="16"/>
+      <c r="C115" s="31"/>
+      <c r="D115" s="16"/>
+      <c r="E115" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="F115" s="8"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="16"/>
+      <c r="B116" s="16"/>
+      <c r="C116" s="31"/>
+      <c r="D116" s="16"/>
+      <c r="E116" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="F116" s="8"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="16"/>
+      <c r="B117" s="16"/>
+      <c r="C117" s="31"/>
+      <c r="D117" s="16"/>
+      <c r="E117" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="F117" s="8"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="16"/>
+      <c r="B118" s="16"/>
+      <c r="C118" s="31"/>
+      <c r="D118" s="16"/>
+      <c r="E118" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="F118" s="8"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="16"/>
+      <c r="B119" s="16"/>
+      <c r="C119" s="31"/>
+      <c r="D119" s="16"/>
+      <c r="E119" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="F119" s="8"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="17"/>
+      <c r="B120" s="17"/>
+      <c r="C120" s="32"/>
+      <c r="D120" s="17"/>
+      <c r="E120" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F120" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="B94:B120"/>
+    <mergeCell ref="C94:C120"/>
+    <mergeCell ref="D108:D120"/>
+    <mergeCell ref="A2:A14"/>
+    <mergeCell ref="B2:B14"/>
+    <mergeCell ref="C2:C14"/>
+    <mergeCell ref="D2:D14"/>
+    <mergeCell ref="D94:D107"/>
+    <mergeCell ref="A94:A107"/>
+    <mergeCell ref="A108:A120"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{BA054F04-F8F1-42D5-8101-D1B0EA85081B}"/>
   </hyperlinks>
